--- a/output/calendario_real.xlsx
+++ b/output/calendario_real.xlsx
@@ -453,12 +453,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-15, 2026-03-16, 2026-03-24</t>
+          <t>2026-03-05, 2026-03-15, 2026-03-21, 2026-03-30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-15, 2026-03-21, 2026-03-30</t>
+          <t>2026-03-07, 2026-03-15, 2026-03-16, 2026-03-21, 2026-03-31</t>
         </is>
       </c>
     </row>
@@ -470,7 +470,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-10, 2026-03-17</t>
+          <t>2026-03-06, 2026-03-11, 2026-03-18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-10, 2026-03-17, 2026-03-25</t>
+          <t>2026-03-07, 2026-03-12, 2026-03-19, 2026-03-25</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-17, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
